--- a/tasks/finalpool/yt-fireship-gform-survey-excel-gcal/groundtruth_workspace/Community_Report.xlsx
+++ b/tasks/finalpool/yt-fireship-gform-survey-excel-gcal/groundtruth_workspace/Community_Report.xlsx
@@ -465,30 +465,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>dQw4w9WgXcQ</t>
+          <t>Nl7aCUsWykg</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>100 Seconds of Code: JavaScript</t>
+          <t>Big Tech in panic mode... Did DeepSeek R1 just pop the AI bubble?</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2850000</v>
+        <v>3878491</v>
       </c>
       <c r="E2" t="n">
-        <v>62000</v>
+        <v>152669</v>
       </c>
       <c r="F2" t="n">
-        <v>120</v>
+        <v>216</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2.18</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="3">
@@ -497,30 +497,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>s2skans2dP4</t>
+          <t>-2k1rcRzsLA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TypeScript in 100 Seconds</t>
+          <t>This free Chinese AI just crushed OpenAI's $200 o1 model...</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2400000</v>
+        <v>3115193</v>
       </c>
       <c r="E3" t="n">
-        <v>55000</v>
+        <v>90213</v>
       </c>
       <c r="F3" t="n">
-        <v>115</v>
+        <v>280</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2.29</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="4">
@@ -529,30 +529,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tn6-PIqc4UM</t>
+          <t>LKCVKw9CzFo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>React in 100 Seconds</t>
+          <t>100+ Linux Things you Need to Know</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2100000</v>
+        <v>2891861</v>
       </c>
       <c r="E4" t="n">
-        <v>48000</v>
+        <v>107006</v>
       </c>
       <c r="F4" t="n">
-        <v>118</v>
+        <v>742</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>Systems</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2.29</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="5">
@@ -561,30 +561,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>aircAruvnKk</t>
+          <t>Iq_r7IcNmUk</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AI is Eating the World - What Does It Actually Do?</t>
+          <t>25 crazy software bugs explained</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1950000</v>
+        <v>2496715</v>
       </c>
       <c r="E5" t="n">
-        <v>41000</v>
+        <v>72881</v>
       </c>
       <c r="F5" t="n">
-        <v>540</v>
+        <v>1009</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2.1</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="6">
@@ -593,30 +593,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5C_HPTJg55E</t>
+          <t>4yDm6xNeYas</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Rust in 100 Seconds</t>
+          <t>Some bad code just broke a billion Windows machines</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1800000</v>
+        <v>2467547</v>
       </c>
       <c r="E6" t="n">
-        <v>43000</v>
+        <v>121950</v>
       </c>
       <c r="F6" t="n">
-        <v>112</v>
+        <v>238</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rust</t>
+          <t>DevOps/Cloud</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2.39</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="7">
@@ -625,22 +625,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rfscVS0vtbw</t>
+          <t>hpwoGjpYygI</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Python in 100 Seconds</t>
+          <t>DeepSeek stole our tech... says OpenAI</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1650000</v>
+        <v>2436569</v>
       </c>
       <c r="E7" t="n">
-        <v>38000</v>
+        <v>92019</v>
       </c>
       <c r="F7" t="n">
-        <v>108</v>
+        <v>291</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.3</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="8">
@@ -657,30 +657,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FHZKLx3ruC8</t>
+          <t>jwnez8HdN7E</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Docker in 100 Seconds</t>
+          <t>Microsoft’s new chip looks like science fiction…</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1350000</v>
+        <v>2329914</v>
       </c>
       <c r="E8" t="n">
-        <v>31000</v>
+        <v>71310</v>
       </c>
       <c r="F8" t="n">
-        <v>110</v>
+        <v>259</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DevOps/Cloud</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2.3</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="9">
@@ -689,30 +689,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>I6ypD4nkynU</t>
+          <t>N3ZGNT5S5IU</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Machine Learning in 100 Seconds</t>
+          <t>Hackers are destroying the Internet's history book right now</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>980000</v>
+        <v>1927279</v>
       </c>
       <c r="E9" t="n">
-        <v>22000</v>
+        <v>107099</v>
       </c>
       <c r="F9" t="n">
-        <v>121</v>
+        <v>261</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Systems</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2.24</v>
+        <v>5.56</v>
       </c>
     </row>
   </sheetData>
@@ -726,7 +726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -754,30 +754,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.18</v>
+        <v>3.42</v>
       </c>
       <c r="C2" t="n">
-        <v>2850000</v>
+        <v>11760167</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>DevOps/Cloud</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.29</v>
+        <v>4.94</v>
       </c>
       <c r="C3" t="n">
-        <v>2400000</v>
+        <v>2467547</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
@@ -786,14 +786,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.29</v>
+        <v>2.92</v>
       </c>
       <c r="C4" t="n">
-        <v>2100000</v>
+        <v>2496715</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -802,49 +802,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Systems</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.22</v>
+        <v>4.63</v>
       </c>
       <c r="C5" t="n">
-        <v>4580000</v>
+        <v>4819140</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Rust</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>DevOps/Cloud</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1350000</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
